--- a/Document/List Masukkan Pelatihan ATWO NTWO.xlsx
+++ b/Document/List Masukkan Pelatihan ATWO NTWO.xlsx
@@ -336,7 +336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,6 +355,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -459,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -506,6 +512,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,9 +827,8 @@
     <col min="2" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="118" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.85546875" style="22" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="15.75" thickBot="1"/>
@@ -842,13 +862,13 @@
       <c r="D3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="3"/>
+      <c r="F3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="2:9" ht="15.75">
       <c r="B4" s="2">
@@ -860,13 +880,13 @@
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3"/>
+      <c r="F4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="15.75">
       <c r="B5" s="18">
@@ -878,13 +898,13 @@
       <c r="D5" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>87</v>
       </c>
       <c r="H5" s="20" t="s">
@@ -902,13 +922,13 @@
       <c r="D6" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="17"/>
+      <c r="F6" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="25"/>
       <c r="H6" s="19"/>
       <c r="I6" s="21"/>
     </row>
@@ -922,13 +942,13 @@
       <c r="D7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="F7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="25" t="s">
         <v>84</v>
       </c>
       <c r="H7" s="20" t="s">
@@ -946,13 +966,13 @@
       <c r="D8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="17"/>
+      <c r="F8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="25"/>
       <c r="H8" s="19"/>
       <c r="I8" s="21"/>
     </row>
@@ -966,13 +986,13 @@
       <c r="D9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="17"/>
+      <c r="F9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="25"/>
       <c r="H9" s="19"/>
       <c r="I9" s="21"/>
     </row>
@@ -986,13 +1006,13 @@
       <c r="D10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="17" t="s">
+      <c r="F10" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H10" s="20" t="s">
@@ -1010,13 +1030,13 @@
       <c r="D11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="17"/>
+      <c r="F11" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="25"/>
       <c r="H11" s="19"/>
       <c r="I11" s="21"/>
     </row>
@@ -1030,13 +1050,13 @@
       <c r="D12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="F12" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H12" s="20" t="s">
@@ -1054,13 +1074,13 @@
       <c r="D13" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="F13" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H13" s="20" t="s">
@@ -1078,13 +1098,13 @@
       <c r="D14" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="F14" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H14" s="20" t="s">
@@ -1102,13 +1122,13 @@
       <c r="D15" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="17" t="s">
+      <c r="F15" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H15" s="20" t="s">
@@ -1126,13 +1146,13 @@
       <c r="D16" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="17" t="s">
+      <c r="F16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H16" s="20" t="s">
@@ -1150,13 +1170,13 @@
       <c r="D17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="17"/>
+      <c r="F17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="25"/>
       <c r="H17" s="19"/>
       <c r="I17" s="21"/>
     </row>
@@ -1170,13 +1190,13 @@
       <c r="D18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="17"/>
+      <c r="F18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="25"/>
       <c r="H18" s="19"/>
       <c r="I18" s="21"/>
     </row>
@@ -1190,13 +1210,13 @@
       <c r="D19" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" s="17"/>
+      <c r="F19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="25"/>
       <c r="H19" s="19"/>
       <c r="I19" s="21"/>
     </row>
@@ -1210,13 +1230,13 @@
       <c r="D20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="17"/>
+      <c r="F20" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="25"/>
       <c r="H20" s="19"/>
       <c r="I20" s="21"/>
     </row>
@@ -1230,13 +1250,13 @@
       <c r="D21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="17"/>
+      <c r="F21" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="25"/>
       <c r="H21" s="19"/>
       <c r="I21" s="21"/>
     </row>
@@ -1250,13 +1270,13 @@
       <c r="D22" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="17"/>
+      <c r="F22" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="25"/>
       <c r="H22" s="19"/>
       <c r="I22" s="21"/>
     </row>
@@ -1270,13 +1290,13 @@
       <c r="D23" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="17" t="s">
+      <c r="F23" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H23" s="20" t="s">
@@ -1294,13 +1314,13 @@
       <c r="D24" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="17" t="s">
+      <c r="F24" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="25" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="20" t="s">
@@ -1318,13 +1338,13 @@
       <c r="D25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="3"/>
+      <c r="F25" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="23"/>
       <c r="I25" s="21"/>
     </row>
     <row r="26" spans="2:9" ht="15.75">
@@ -1337,13 +1357,13 @@
       <c r="D26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="23"/>
     </row>
     <row r="27" spans="2:9" ht="15.75">
       <c r="B27" s="2">
@@ -1355,13 +1375,13 @@
       <c r="D27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="23"/>
     </row>
     <row r="28" spans="2:9" ht="15.75">
       <c r="B28" s="2">
@@ -1373,13 +1393,13 @@
       <c r="D28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="3"/>
+      <c r="G28" s="23"/>
     </row>
     <row r="29" spans="2:9" ht="15.75">
       <c r="B29" s="2">
@@ -1391,13 +1411,13 @@
       <c r="D29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="3"/>
+      <c r="G29" s="23"/>
     </row>
     <row r="30" spans="2:9" ht="15.75">
       <c r="B30" s="2">
@@ -1409,13 +1429,13 @@
       <c r="D30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="3"/>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" spans="2:9" ht="15.75">
       <c r="B31" s="2">
@@ -1427,13 +1447,13 @@
       <c r="D31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="3"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="2:9" ht="16.5" thickBot="1">
       <c r="B32" s="2">
@@ -1445,13 +1465,13 @@
       <c r="D32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="4"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="2:4" ht="16.5" thickBot="1">
       <c r="B33" s="7">
